--- a/historical_reference_data/7-10-2025_Pregnancy_Chip_10/cleaned/UNKNOWN950104_041744_0001VRP_PREGNANCY_CHIP_TEST_10_CLEANED.xlsx
+++ b/historical_reference_data/7-10-2025_Pregnancy_Chip_10/cleaned/UNKNOWN950104_041744_0001VRP_PREGNANCY_CHIP_TEST_10_CLEANED.xlsx
@@ -614,7 +614,11 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
       <c r="C2" t="n">
         <v>15</v>
       </c>
@@ -722,7 +726,11 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>START</t>
+        </is>
+      </c>
       <c r="C3" t="n">
         <v>77</v>
       </c>
@@ -830,7 +838,11 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C4" t="n">
         <v>87</v>
       </c>
@@ -938,7 +950,11 @@
       <c r="A5" t="n">
         <v>3</v>
       </c>
-      <c r="B5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>PURGE</t>
+        </is>
+      </c>
       <c r="C5" t="n">
         <v>40089</v>
       </c>
@@ -1046,7 +1062,11 @@
       <c r="A6" t="n">
         <v>4</v>
       </c>
-      <c r="B6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
       <c r="C6" t="n">
         <v>40099</v>
       </c>
@@ -1154,7 +1174,11 @@
       <c r="A7" t="n">
         <v>5</v>
       </c>
-      <c r="B7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>CHANGE</t>
+        </is>
+      </c>
       <c r="C7" t="n">
         <v>40161</v>
       </c>
@@ -1262,7 +1286,11 @@
       <c r="A8" t="n">
         <v>6</v>
       </c>
-      <c r="B8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
       <c r="C8" t="n">
         <v>40171</v>
       </c>
@@ -1370,7 +1398,11 @@
       <c r="A9" t="n">
         <v>7</v>
       </c>
-      <c r="B9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C9" t="n">
         <v>40233</v>
       </c>
@@ -1478,7 +1510,11 @@
       <c r="A10" t="n">
         <v>7</v>
       </c>
-      <c r="B10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>BREATH</t>
+        </is>
+      </c>
       <c r="C10" t="n">
         <v>50233</v>
       </c>
@@ -1586,7 +1622,11 @@
       <c r="A11" t="n">
         <v>8</v>
       </c>
-      <c r="B11" t="inlineStr"/>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
       <c r="C11" t="n">
         <v>50243</v>
       </c>
@@ -1694,7 +1734,11 @@
       <c r="A12" t="n">
         <v>9</v>
       </c>
-      <c r="B12" t="inlineStr"/>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>CHANGE</t>
+        </is>
+      </c>
       <c r="C12" t="n">
         <v>50305</v>
       </c>
@@ -1802,7 +1846,11 @@
       <c r="A13" t="n">
         <v>10</v>
       </c>
-      <c r="B13" t="inlineStr"/>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
       <c r="C13" t="n">
         <v>50315</v>
       </c>
@@ -1910,7 +1958,11 @@
       <c r="A14" t="n">
         <v>11</v>
       </c>
-      <c r="B14" t="inlineStr"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C14" t="n">
         <v>50377</v>
       </c>
@@ -2018,7 +2070,11 @@
       <c r="A15" t="n">
         <v>11</v>
       </c>
-      <c r="B15" t="inlineStr"/>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>POST</t>
+        </is>
+      </c>
       <c r="C15" t="n">
         <v>90377</v>
       </c>
@@ -2126,7 +2182,11 @@
       <c r="A16" t="n">
         <v>12</v>
       </c>
-      <c r="B16" t="inlineStr"/>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
       <c r="C16" t="n">
         <v>90387</v>
       </c>
@@ -2234,7 +2294,11 @@
       <c r="A17" t="n">
         <v>13</v>
       </c>
-      <c r="B17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>CLOSE</t>
+        </is>
+      </c>
       <c r="C17" t="n">
         <v>90397</v>
       </c>
